--- a/artfynd/A 64885-2023 artfynd.xlsx
+++ b/artfynd/A 64885-2023 artfynd.xlsx
@@ -4487,7 +4487,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>117766685</v>
+        <v>117766683</v>
       </c>
       <c r="B36" t="n">
         <v>97836</v>
@@ -4522,7 +4522,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4531,10 +4531,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>574917</v>
+        <v>574844</v>
       </c>
       <c r="R36" t="n">
-        <v>6399278</v>
+        <v>6399227</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4598,7 +4598,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>117766683</v>
+        <v>117766681</v>
       </c>
       <c r="B37" t="n">
         <v>97836</v>
@@ -4633,7 +4633,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4642,10 +4642,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>574844</v>
+        <v>574916</v>
       </c>
       <c r="R37" t="n">
-        <v>6399227</v>
+        <v>6399276</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4709,7 +4709,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>117766681</v>
+        <v>117766687</v>
       </c>
       <c r="B38" t="n">
         <v>97836</v>
@@ -4753,10 +4753,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>574916</v>
+        <v>574932</v>
       </c>
       <c r="R38" t="n">
-        <v>6399276</v>
+        <v>6399269</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4820,7 +4820,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>117766687</v>
+        <v>117766685</v>
       </c>
       <c r="B39" t="n">
         <v>97836</v>
@@ -4855,7 +4855,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>574932</v>
+        <v>574917</v>
       </c>
       <c r="R39" t="n">
-        <v>6399269</v>
+        <v>6399278</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>

--- a/artfynd/A 64885-2023 artfynd.xlsx
+++ b/artfynd/A 64885-2023 artfynd.xlsx
@@ -4487,10 +4487,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>117766683</v>
+        <v>117766685</v>
       </c>
       <c r="B36" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4522,7 +4522,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4531,10 +4531,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>574844</v>
+        <v>574917</v>
       </c>
       <c r="R36" t="n">
-        <v>6399227</v>
+        <v>6399278</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4598,10 +4598,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>117766681</v>
+        <v>117766687</v>
       </c>
       <c r="B37" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4642,10 +4642,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>574916</v>
+        <v>574932</v>
       </c>
       <c r="R37" t="n">
-        <v>6399276</v>
+        <v>6399269</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4709,10 +4709,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>117766687</v>
+        <v>117766683</v>
       </c>
       <c r="B38" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4744,7 +4744,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4753,10 +4753,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>574932</v>
+        <v>574844</v>
       </c>
       <c r="R38" t="n">
-        <v>6399269</v>
+        <v>6399227</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4820,10 +4820,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>117766685</v>
+        <v>117766681</v>
       </c>
       <c r="B39" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4855,7 +4855,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>574917</v>
+        <v>574916</v>
       </c>
       <c r="R39" t="n">
-        <v>6399278</v>
+        <v>6399276</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>

--- a/artfynd/A 64885-2023 artfynd.xlsx
+++ b/artfynd/A 64885-2023 artfynd.xlsx
@@ -4934,7 +4934,7 @@
         <v>121172441</v>
       </c>
       <c r="B40" t="n">
-        <v>57501</v>
+        <v>57504</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>

--- a/artfynd/A 64885-2023 artfynd.xlsx
+++ b/artfynd/A 64885-2023 artfynd.xlsx
@@ -4934,7 +4934,7 @@
         <v>121172441</v>
       </c>
       <c r="B40" t="n">
-        <v>57504</v>
+        <v>57507</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>

--- a/artfynd/A 64885-2023 artfynd.xlsx
+++ b/artfynd/A 64885-2023 artfynd.xlsx
@@ -4934,7 +4934,7 @@
         <v>121172441</v>
       </c>
       <c r="B40" t="n">
-        <v>57507</v>
+        <v>57508</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
